--- a/ADVシナリオ管理.xlsx
+++ b/ADVシナリオ管理.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pa-sa\Documents\GitHub\song-for-life-prototype\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_57E55EF38400B18E55E1FF02685AC0A8556D2460" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10030568-177B-4333-8D35-D2CA8885D305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="15660" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ADVシナリオ管理" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="256">
   <si>
     <t>Tap</t>
   </si>
@@ -857,9 +857,6 @@
     <t>あなたなら、抗えるわ</t>
   </si>
   <si>
-    <t>存在波測定ブース／暗め</t>
-  </si>
-  <si>
     <t>MinaバストアップをゆっくりFADE IN</t>
   </si>
   <si>
@@ -1006,6 +1003,17 @@
   </si>
   <si>
     <t>体験版終了。候補生『凛』の名前を画面中央に大きく見せて締める</t>
+  </si>
+  <si>
+    <t>存在波測定ブース</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>bg_ad_road</t>
+  </si>
+  <si>
+    <t>bg_ad_road</t>
+    <phoneticPr fontId="5"/>
   </si>
 </sst>
 </file>
@@ -1262,7 +1270,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1428,6 +1436,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1648,7 +1659,7 @@
     <col min="1" max="1" width="4.5" style="50" customWidth="1"/>
     <col min="2" max="2" width="23.25" customWidth="1"/>
     <col min="3" max="3" width="18.33203125" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="4" max="4" width="73.58203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="8" width="8.33203125" customWidth="1"/>
     <col min="9" max="9" width="39.08203125" customWidth="1"/>
@@ -3901,7 +3912,9 @@
       <c r="I64" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="J64" s="40"/>
+      <c r="J64" s="40" t="s">
+        <v>255</v>
+      </c>
       <c r="K64" s="40"/>
       <c r="L64" s="40"/>
       <c r="M64" s="40"/>
@@ -3920,8 +3933,8 @@
       <c r="D65" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="E65" s="40" t="s">
-        <v>194</v>
+      <c r="E65" s="56" t="s">
+        <v>253</v>
       </c>
       <c r="F65" s="40" t="s">
         <v>65</v>
@@ -3931,7 +3944,9 @@
       </c>
       <c r="H65" s="40"/>
       <c r="I65" s="40"/>
-      <c r="J65" s="40"/>
+      <c r="J65" s="40" t="s">
+        <v>255</v>
+      </c>
       <c r="K65" s="40" t="s">
         <v>88</v>
       </c>
@@ -3954,8 +3969,8 @@
       <c r="D66" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="E66" s="40" t="s">
-        <v>194</v>
+      <c r="E66" s="56" t="s">
+        <v>253</v>
       </c>
       <c r="F66" s="40" t="s">
         <v>18</v>
@@ -3988,20 +4003,20 @@
       <c r="D67" s="40" t="s">
         <v>203</v>
       </c>
-      <c r="E67" s="40" t="s">
+      <c r="E67" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="F67" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="I67" s="40" t="s">
         <v>204</v>
-      </c>
-      <c r="F67" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="G67" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="H67" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="I67" s="40" t="s">
-        <v>205</v>
       </c>
       <c r="J67" s="40" t="s">
         <v>162</v>
@@ -4009,10 +4024,10 @@
       <c r="K67" s="40"/>
       <c r="L67" s="40"/>
       <c r="M67" s="40" t="s">
+        <v>205</v>
+      </c>
+      <c r="N67" s="40" t="s">
         <v>206</v>
-      </c>
-      <c r="N67" s="40" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="18.649999999999999" customHeight="1">
@@ -4026,28 +4041,32 @@
         <v>202</v>
       </c>
       <c r="D68" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="E68" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="F68" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="G68" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="H68" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="I68" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="E68" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="F68" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="G68" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="H68" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="I68" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="J68" s="40"/>
-      <c r="K68" s="40"/>
+      <c r="J68" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="K68" s="40" t="s">
+        <v>88</v>
+      </c>
       <c r="L68" s="40"/>
       <c r="M68" s="40" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N68" s="40"/>
     </row>
@@ -4062,30 +4081,32 @@
         <v>5</v>
       </c>
       <c r="D69" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="E69" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="F69" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="G69" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="I69" s="40" t="s">
         <v>210</v>
       </c>
-      <c r="E69" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="F69" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="G69" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="H69" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="I69" s="40" t="s">
-        <v>211</v>
-      </c>
-      <c r="J69" s="40"/>
+      <c r="J69" s="40" t="s">
+        <v>255</v>
+      </c>
       <c r="K69" s="40" t="s">
         <v>88</v>
       </c>
       <c r="L69" s="40"/>
       <c r="M69" s="40" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N69" s="40"/>
     </row>
@@ -4100,30 +4121,32 @@
         <v>5</v>
       </c>
       <c r="D70" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="E70" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="F70" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="G70" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="H70" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="I70" s="40" t="s">
         <v>213</v>
       </c>
-      <c r="E70" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="F70" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="G70" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="H70" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="I70" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="J70" s="40"/>
+      <c r="J70" s="40" t="s">
+        <v>255</v>
+      </c>
       <c r="K70" s="40" t="s">
         <v>88</v>
       </c>
       <c r="L70" s="40"/>
       <c r="M70" s="40" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N70" s="40"/>
     </row>
@@ -4132,16 +4155,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C71" s="44" t="s">
         <v>164</v>
       </c>
       <c r="D71" s="44" t="s">
+        <v>215</v>
+      </c>
+      <c r="E71" s="44" t="s">
         <v>216</v>
-      </c>
-      <c r="E71" s="44" t="s">
-        <v>217</v>
       </c>
       <c r="F71" s="44" t="s">
         <v>18</v>
@@ -4151,7 +4174,7 @@
       </c>
       <c r="H71" s="44"/>
       <c r="I71" s="44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J71" s="44"/>
       <c r="K71" s="44"/>
@@ -4164,13 +4187,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C72" s="44" t="s">
         <v>6</v>
       </c>
       <c r="D72" s="44" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E72" s="44" t="s">
         <v>130</v>
@@ -4183,7 +4206,7 @@
       </c>
       <c r="H72" s="44"/>
       <c r="I72" s="44" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J72" s="44"/>
       <c r="K72" s="44" t="s">
@@ -4200,13 +4223,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C73" s="44" t="s">
         <v>6</v>
       </c>
       <c r="D73" s="44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E73" s="44" t="s">
         <v>130</v>
@@ -4219,7 +4242,7 @@
       </c>
       <c r="H73" s="44"/>
       <c r="I73" s="44" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J73" s="44"/>
       <c r="K73" s="44" t="s">
@@ -4236,13 +4259,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C74" s="44" t="s">
         <v>6</v>
       </c>
       <c r="D74" s="44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E74" s="44" t="s">
         <v>130</v>
@@ -4255,7 +4278,7 @@
       </c>
       <c r="H74" s="44"/>
       <c r="I74" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J74" s="44"/>
       <c r="K74" s="44" t="s">
@@ -4266,7 +4289,7 @@
       </c>
       <c r="M74" s="44"/>
       <c r="N74" s="44" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="75" spans="1:14" ht="18.649999999999999" customHeight="1">
@@ -4274,13 +4297,13 @@
         <v>74</v>
       </c>
       <c r="B75" s="44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C75" s="44" t="s">
         <v>5</v>
       </c>
       <c r="D75" s="44" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E75" s="44" t="s">
         <v>130</v>
@@ -4293,7 +4316,7 @@
       </c>
       <c r="H75" s="44"/>
       <c r="I75" s="44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J75" s="44"/>
       <c r="K75" s="44" t="s">
@@ -4310,13 +4333,13 @@
         <v>75</v>
       </c>
       <c r="B76" s="44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C76" s="44" t="s">
         <v>5</v>
       </c>
       <c r="D76" s="44" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E76" s="44" t="s">
         <v>130</v>
@@ -4329,7 +4352,7 @@
       </c>
       <c r="H76" s="44"/>
       <c r="I76" s="44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J76" s="44"/>
       <c r="K76" s="44" t="s">
@@ -4340,7 +4363,7 @@
       </c>
       <c r="M76" s="44"/>
       <c r="N76" s="44" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="18.649999999999999" customHeight="1">
@@ -4348,16 +4371,16 @@
         <v>76</v>
       </c>
       <c r="B77" s="45" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C77" s="45" t="s">
         <v>164</v>
       </c>
       <c r="D77" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="E77" s="45" t="s">
         <v>231</v>
-      </c>
-      <c r="E77" s="45" t="s">
-        <v>232</v>
       </c>
       <c r="F77" s="45" t="s">
         <v>18</v>
@@ -4367,14 +4390,14 @@
       </c>
       <c r="H77" s="45"/>
       <c r="I77" s="45" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J77" s="45"/>
       <c r="K77" s="45"/>
       <c r="L77" s="45"/>
       <c r="M77" s="45"/>
       <c r="N77" s="45" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -4451,7 +4474,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20">
       <c r="A1" s="55" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B1" s="55"/>
       <c r="C1" s="55"/>
@@ -4459,16 +4482,16 @@
     </row>
     <row r="3" spans="1:4" ht="21.4" customHeight="1">
       <c r="A3" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="C3" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="D3" s="24" t="s">
         <v>236</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="21.4" customHeight="1">
@@ -4476,13 +4499,13 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="21.4" customHeight="1">
@@ -4490,13 +4513,13 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="21.4" customHeight="1">
@@ -4504,13 +4527,13 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="21.4" customHeight="1">
@@ -4518,13 +4541,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="21.4" customHeight="1">
@@ -4532,13 +4555,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
   </sheetData>
